--- a/Web page.xlsx
+++ b/Web page.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Hp\Documents\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{F37A7E82-BDFD-4135-B29E-463F0CC562B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{35ACF74C-7966-4987-A5A7-2E4C0D439DEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="60">
   <si>
     <t>Test Case Desc</t>
   </si>
@@ -29,9 +29,6 @@
   </si>
   <si>
     <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Version</t>
   </si>
   <si>
     <t xml:space="preserve">Tester's Name </t>
@@ -74,25 +71,137 @@
     <t>TC_practical_002</t>
   </si>
   <si>
-    <t>Test the functionality of Windows Calculator Application</t>
-  </si>
-  <si>
     <t>2.0</t>
-  </si>
-  <si>
-    <t>Test Case IDA1:J19D34A1:J39A1:J20D34A1:J39A1:J22D34A1:J39A1:J24D34A1:J39A1:J29A1:J39+A1:J39</t>
   </si>
   <si>
     <t>Aishwarya Gunjarkar</t>
   </si>
   <si>
-    <t>\</t>
+    <t>Verify that 10 is entered successfully in A field.</t>
   </si>
   <si>
-    <t>Test web page for addition on browser.</t>
+    <t>Enter a valid number  in B field, e.g., 20.</t>
   </si>
   <si>
-    <t>Open the google chrome browser.</t>
+    <t>Verify that  20 is entered successfully in B  ffield.</t>
+  </si>
+  <si>
+    <t>Click  on the Add button.</t>
+  </si>
+  <si>
+    <t>Verify that the result  30 is displayed.</t>
+  </si>
+  <si>
+    <t>Verify that the result 10 is displayed.</t>
+  </si>
+  <si>
+    <t>Verify that the result 5 is displayed.</t>
+  </si>
+  <si>
+    <t>Enter  0 in A field and 0 in b field ,click on Add button.</t>
+  </si>
+  <si>
+    <t>Verify that the result is 0 .</t>
+  </si>
+  <si>
+    <t>Verify that the result is 10.</t>
+  </si>
+  <si>
+    <t>Enter 10 in A and (-20) in B . Click on Add button.</t>
+  </si>
+  <si>
+    <t>Verify that the result is (-10).</t>
+  </si>
+  <si>
+    <t>Verify that the result is (-30).</t>
+  </si>
+  <si>
+    <t>Enter 10.5 in A field and 20.5 in B field. Click on Add button.</t>
+  </si>
+  <si>
+    <t>Verify that the result is 31.</t>
+  </si>
+  <si>
+    <t>Verify that a validation message is displayed.</t>
+  </si>
+  <si>
+    <t>Enter 35 in A field and leave  B field empty. Click Add button.</t>
+  </si>
+  <si>
+    <t>Leave  both A field and B field empty. Click on Add button.</t>
+  </si>
+  <si>
+    <t>Enter abc in A field  and 5  in B field . Click on Add button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Verify that invalid input is rejected. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Enter 15  in A field  and abc in B field. Click on Add button. </t>
+  </si>
+  <si>
+    <t>Enter 010 in A field and 5 in B field. Click on Add button.</t>
+  </si>
+  <si>
+    <t>Verify that the result is 15 .</t>
+  </si>
+  <si>
+    <t>Enter 10 in A field and 020 in B field. Click on Add button.</t>
+  </si>
+  <si>
+    <t>Verify that the result is 30.</t>
+  </si>
+  <si>
+    <t>Enter (-2.5) in A field and 1.5 in B field . Click on  Add button.</t>
+  </si>
+  <si>
+    <t>Verify that the result is (-1).</t>
+  </si>
+  <si>
+    <t>Verify that the result is 0.</t>
+  </si>
+  <si>
+    <t>Gauri Mahalle</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Open  simple user interface for addition of  two numbers.
+</t>
+  </si>
+  <si>
+    <t>Verify that user interface should be opened.</t>
+  </si>
+  <si>
+    <t>Test cases for testing simple user interface for additon  of two numbers.</t>
+  </si>
+  <si>
+    <t>User interface for adding two numbers.</t>
+  </si>
+  <si>
+    <t>Test the web page addition of two numbers.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Test Case </t>
+  </si>
+  <si>
+    <t>1) Enter 5 in A field and 0 in B field.                            2) Click on the Add button.</t>
+  </si>
+  <si>
+    <t>Leave A field  empty  and  enter 16 in B . Click  Add button.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Enter  0 in A field and 10 in B field.                                                   2) Click  on the Add button.  </t>
+  </si>
+  <si>
+    <t xml:space="preserve">1) Enter (-10) in A field  and  20 in  field .                                                  2) Click Add button. </t>
+  </si>
+  <si>
+    <t>Enter (-10) in A field and  (-20) in B field. Click on Add button.</t>
+  </si>
+  <si>
+    <t>Enter a valid number in A field,    e.g., 10.</t>
+  </si>
+  <si>
+    <t>Enter  5 in A field  and (-5) in B field.</t>
   </si>
 </sst>
 </file>
@@ -499,7 +608,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -577,27 +686,38 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
@@ -609,32 +729,24 @@
     <xf numFmtId="0" fontId="5" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="17" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -650,6 +762,56 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>3</xdr:col>
+      <xdr:colOff>238125</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>484793</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>1200150</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>2000250</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF2656DE-4C34-89B8-0FE4-C4B90353B550}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill rotWithShape="1">
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:srcRect l="1" t="4310" r="1664" b="29895"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="4257675" y="3942368"/>
+          <a:ext cx="2409825" cy="1515457"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -853,37 +1015,39 @@
   <dimension ref="A1:Y994"/>
   <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="1" customWidth="1"/>
-    <col min="2" max="5" width="21.7109375" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.7109375" style="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" style="1" customWidth="1"/>
+    <col min="3" max="3" width="30.140625" style="1" customWidth="1"/>
+    <col min="4" max="5" width="21.7109375" style="1" customWidth="1"/>
     <col min="6" max="6" width="6.28515625" style="1" customWidth="1"/>
-    <col min="7" max="7" width="7" style="1" customWidth="1"/>
+    <col min="7" max="7" width="23.140625" style="1" customWidth="1"/>
     <col min="8" max="8" width="6.28515625" style="1" customWidth="1"/>
     <col min="9" max="9" width="4.5703125" style="1" customWidth="1"/>
-    <col min="10" max="10" width="16.42578125" style="1" customWidth="1"/>
+    <col min="10" max="10" width="18.28515625" style="1" customWidth="1"/>
     <col min="11" max="11" width="13.7109375" style="1" customWidth="1"/>
     <col min="12" max="25" width="9.140625" style="1" customWidth="1"/>
     <col min="26" max="16384" width="12.5703125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="49" t="s">
-        <v>19</v>
+    <row r="1" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="27" t="s">
+        <v>52</v>
       </c>
-      <c r="B1" s="45"/>
+      <c r="B1" s="28"/>
       <c r="C1" s="4" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="D1" s="5" t="s">
         <v>0</v>
       </c>
       <c r="E1" s="6"/>
-      <c r="F1" s="50" t="s">
-        <v>17</v>
+      <c r="F1" s="29" t="s">
+        <v>49</v>
       </c>
-      <c r="G1" s="46"/>
-      <c r="H1" s="46"/>
-      <c r="I1" s="46"/>
-      <c r="J1" s="47"/>
+      <c r="G1" s="30"/>
+      <c r="H1" s="30"/>
+      <c r="I1" s="30"/>
+      <c r="J1" s="31"/>
       <c r="K1" s="2"/>
       <c r="L1" s="2"/>
       <c r="M1" s="2"/>
@@ -900,26 +1064,26 @@
       <c r="X1" s="2"/>
       <c r="Y1" s="2"/>
     </row>
-    <row r="2" spans="1:25" ht="37.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="51" t="s">
+    <row r="2" spans="1:25" ht="21" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="32" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="32"/>
+      <c r="B2" s="33"/>
       <c r="C2" s="7" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D2" s="8" t="s">
         <v>2</v>
       </c>
       <c r="E2" s="9"/>
-      <c r="F2" s="31"/>
-      <c r="G2" s="32"/>
-      <c r="H2" s="52" t="s">
-        <v>3</v>
+      <c r="F2" s="34" t="s">
+        <v>46</v>
       </c>
-      <c r="I2" s="32"/>
+      <c r="G2" s="33"/>
+      <c r="H2" s="34"/>
+      <c r="I2" s="33"/>
       <c r="J2" s="10" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="K2" s="2"/>
       <c r="L2" s="2"/>
@@ -938,21 +1102,21 @@
       <c r="Y2" s="2"/>
     </row>
     <row r="3" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="51" t="s">
+      <c r="A3" s="32" t="s">
+        <v>3</v>
+      </c>
+      <c r="B3" s="33"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="8" t="s">
         <v>4</v>
       </c>
-      <c r="B3" s="32"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="8" t="s">
+      <c r="E3" s="9"/>
+      <c r="F3" s="35"/>
+      <c r="G3" s="33"/>
+      <c r="H3" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="E3" s="9"/>
-      <c r="F3" s="53"/>
-      <c r="G3" s="32"/>
-      <c r="H3" s="52" t="s">
-        <v>6</v>
-      </c>
-      <c r="I3" s="32"/>
+      <c r="I3" s="33"/>
       <c r="J3" s="11"/>
       <c r="K3" s="2"/>
       <c r="L3" s="2"/>
@@ -999,23 +1163,23 @@
     </row>
     <row r="5" spans="1:25" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="B5" s="39" t="s">
         <v>7</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="C5" s="37"/>
+      <c r="D5" s="33"/>
+      <c r="E5" s="16"/>
+      <c r="F5" s="17" t="s">
+        <v>6</v>
+      </c>
+      <c r="G5" s="36" t="s">
         <v>8</v>
       </c>
-      <c r="C5" s="54"/>
-      <c r="D5" s="32"/>
-      <c r="E5" s="16"/>
-      <c r="F5" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="G5" s="52" t="s">
-        <v>9</v>
-      </c>
-      <c r="H5" s="54"/>
-      <c r="I5" s="54"/>
-      <c r="J5" s="55"/>
+      <c r="H5" s="37"/>
+      <c r="I5" s="37"/>
+      <c r="J5" s="38"/>
       <c r="K5" s="2"/>
       <c r="L5" s="2"/>
       <c r="M5" s="2"/>
@@ -1036,17 +1200,19 @@
       <c r="A6" s="18">
         <v>1</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="54"/>
-      <c r="D6" s="32"/>
+      <c r="B6" s="34" t="s">
+        <v>50</v>
+      </c>
+      <c r="C6" s="37"/>
+      <c r="D6" s="33"/>
       <c r="E6" s="7"/>
       <c r="F6" s="19">
         <v>1</v>
       </c>
-      <c r="G6" s="31"/>
-      <c r="H6" s="54"/>
-      <c r="I6" s="54"/>
-      <c r="J6" s="55"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="37"/>
+      <c r="I6" s="37"/>
+      <c r="J6" s="38"/>
       <c r="K6" s="2"/>
       <c r="L6" s="2"/>
       <c r="M6" s="2"/>
@@ -1067,17 +1233,17 @@
       <c r="A7" s="18">
         <v>2</v>
       </c>
-      <c r="B7" s="31"/>
-      <c r="C7" s="54"/>
-      <c r="D7" s="32"/>
+      <c r="B7" s="34"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="33"/>
       <c r="E7" s="7"/>
       <c r="F7" s="19">
         <v>2</v>
       </c>
-      <c r="G7" s="31"/>
-      <c r="H7" s="54"/>
-      <c r="I7" s="54"/>
-      <c r="J7" s="55"/>
+      <c r="G7" s="34"/>
+      <c r="H7" s="37"/>
+      <c r="I7" s="37"/>
+      <c r="J7" s="38"/>
       <c r="K7" s="2"/>
       <c r="L7" s="2"/>
       <c r="M7" s="2"/>
@@ -1098,17 +1264,17 @@
       <c r="A8" s="18">
         <v>3</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="54"/>
-      <c r="D8" s="32"/>
+      <c r="B8" s="34"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="33"/>
       <c r="E8" s="7"/>
       <c r="F8" s="19">
         <v>3</v>
       </c>
-      <c r="G8" s="31"/>
-      <c r="H8" s="54"/>
-      <c r="I8" s="54"/>
-      <c r="J8" s="55"/>
+      <c r="G8" s="34"/>
+      <c r="H8" s="37"/>
+      <c r="I8" s="37"/>
+      <c r="J8" s="38"/>
       <c r="K8" s="2"/>
       <c r="L8" s="2"/>
       <c r="M8" s="2"/>
@@ -1129,17 +1295,17 @@
       <c r="A9" s="20">
         <v>4</v>
       </c>
-      <c r="B9" s="33"/>
-      <c r="C9" s="39"/>
-      <c r="D9" s="34"/>
+      <c r="B9" s="40"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="42"/>
       <c r="E9" s="21"/>
       <c r="F9" s="22">
         <v>4</v>
       </c>
-      <c r="G9" s="33"/>
-      <c r="H9" s="39"/>
-      <c r="I9" s="39"/>
-      <c r="J9" s="40"/>
+      <c r="G9" s="40"/>
+      <c r="H9" s="41"/>
+      <c r="I9" s="41"/>
+      <c r="J9" s="43"/>
       <c r="K9" s="3"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -1185,19 +1351,19 @@
     </row>
     <row r="11" spans="1:25" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="24" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
-      <c r="B11" s="41" t="s">
-        <v>22</v>
+      <c r="B11" s="44" t="s">
+        <v>51</v>
       </c>
-      <c r="C11" s="42"/>
-      <c r="D11" s="42"/>
-      <c r="E11" s="42"/>
-      <c r="F11" s="42"/>
-      <c r="G11" s="42"/>
-      <c r="H11" s="42"/>
-      <c r="I11" s="42"/>
-      <c r="J11" s="42"/>
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="45"/>
+      <c r="F11" s="45"/>
+      <c r="G11" s="45"/>
+      <c r="H11" s="45"/>
+      <c r="I11" s="45"/>
+      <c r="J11" s="45"/>
       <c r="K11" s="2"/>
       <c r="L11" s="2"/>
       <c r="M11" s="2"/>
@@ -1216,15 +1382,15 @@
     </row>
     <row r="12" spans="1:25" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="25"/>
-      <c r="B12" s="43"/>
-      <c r="C12" s="42"/>
-      <c r="D12" s="42"/>
-      <c r="E12" s="42"/>
-      <c r="F12" s="42"/>
-      <c r="G12" s="42"/>
-      <c r="H12" s="42"/>
-      <c r="I12" s="42"/>
-      <c r="J12" s="42"/>
+      <c r="B12" s="46"/>
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="45"/>
+      <c r="F12" s="45"/>
+      <c r="G12" s="45"/>
+      <c r="H12" s="45"/>
+      <c r="I12" s="45"/>
+      <c r="J12" s="45"/>
       <c r="K12" s="2"/>
       <c r="L12" s="2"/>
       <c r="M12" s="2"/>
@@ -1270,25 +1436,25 @@
     </row>
     <row r="14" spans="1:25" ht="18" x14ac:dyDescent="0.25">
       <c r="A14" s="26" t="s">
+        <v>10</v>
+      </c>
+      <c r="B14" s="47" t="s">
         <v>11</v>
       </c>
-      <c r="B14" s="44" t="s">
+      <c r="C14" s="28"/>
+      <c r="D14" s="47" t="s">
         <v>12</v>
       </c>
-      <c r="C14" s="45"/>
-      <c r="D14" s="44" t="s">
+      <c r="E14" s="28"/>
+      <c r="F14" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="E14" s="45"/>
-      <c r="F14" s="44" t="s">
+      <c r="G14" s="30"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="47" t="s">
         <v>14</v>
       </c>
-      <c r="G14" s="46"/>
-      <c r="H14" s="45"/>
-      <c r="I14" s="44" t="s">
-        <v>15</v>
-      </c>
-      <c r="J14" s="47"/>
+      <c r="J14" s="31"/>
       <c r="K14" s="2"/>
       <c r="L14" s="2"/>
       <c r="M14" s="2"/>
@@ -1305,21 +1471,23 @@
       <c r="X14" s="2"/>
       <c r="Y14" s="2"/>
     </row>
-    <row r="15" spans="1:25" ht="33" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:25" ht="164.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="18">
         <v>1</v>
       </c>
-      <c r="B15" s="48" t="s">
-        <v>23</v>
+      <c r="B15" s="52" t="s">
+        <v>47</v>
       </c>
-      <c r="C15" s="48"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="32"/>
-      <c r="F15" s="27"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="30"/>
+      <c r="C15" s="53"/>
+      <c r="D15" s="34" t="s">
+        <v>48</v>
+      </c>
+      <c r="E15" s="33"/>
+      <c r="F15" s="48"/>
+      <c r="G15" s="49"/>
+      <c r="H15" s="50"/>
+      <c r="I15" s="48"/>
+      <c r="J15" s="51"/>
       <c r="K15" s="2"/>
       <c r="L15" s="2"/>
       <c r="M15" s="2"/>
@@ -1336,19 +1504,23 @@
       <c r="X15" s="2"/>
       <c r="Y15" s="2"/>
     </row>
-    <row r="16" spans="1:25" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:25" ht="38.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="18">
         <v>2</v>
       </c>
-      <c r="B16" s="31"/>
-      <c r="C16" s="32"/>
-      <c r="D16" s="31"/>
-      <c r="E16" s="32"/>
-      <c r="F16" s="27"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="29"/>
-      <c r="I16" s="27"/>
-      <c r="J16" s="30"/>
+      <c r="B16" s="34" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="33"/>
+      <c r="D16" s="34" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="33"/>
+      <c r="F16" s="48"/>
+      <c r="G16" s="49"/>
+      <c r="H16" s="50"/>
+      <c r="I16" s="48"/>
+      <c r="J16" s="51"/>
       <c r="K16" s="2"/>
       <c r="L16" s="2"/>
       <c r="M16" s="2"/>
@@ -1365,19 +1537,23 @@
       <c r="X16" s="2"/>
       <c r="Y16" s="2"/>
     </row>
-    <row r="17" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="18">
         <v>3</v>
       </c>
-      <c r="B17" s="31"/>
-      <c r="C17" s="32"/>
-      <c r="D17" s="31"/>
-      <c r="E17" s="32"/>
-      <c r="F17" s="27"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="29"/>
-      <c r="I17" s="27"/>
-      <c r="J17" s="30"/>
+      <c r="B17" s="34" t="s">
+        <v>19</v>
+      </c>
+      <c r="C17" s="33"/>
+      <c r="D17" s="34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E17" s="33"/>
+      <c r="F17" s="48"/>
+      <c r="G17" s="49"/>
+      <c r="H17" s="50"/>
+      <c r="I17" s="48"/>
+      <c r="J17" s="51"/>
       <c r="K17" s="2"/>
       <c r="L17" s="2"/>
       <c r="M17" s="2"/>
@@ -1394,19 +1570,23 @@
       <c r="X17" s="2"/>
       <c r="Y17" s="2"/>
     </row>
-    <row r="18" spans="1:25" ht="45.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="18">
         <v>4</v>
       </c>
-      <c r="B18" s="31"/>
-      <c r="C18" s="32"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="32"/>
-      <c r="F18" s="27"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="29"/>
-      <c r="I18" s="27"/>
-      <c r="J18" s="30"/>
+      <c r="B18" s="34" t="s">
+        <v>21</v>
+      </c>
+      <c r="C18" s="33"/>
+      <c r="D18" s="34" t="s">
+        <v>22</v>
+      </c>
+      <c r="E18" s="33"/>
+      <c r="F18" s="48"/>
+      <c r="G18" s="49"/>
+      <c r="H18" s="50"/>
+      <c r="I18" s="48"/>
+      <c r="J18" s="51"/>
       <c r="K18" s="2"/>
       <c r="L18" s="2"/>
       <c r="M18" s="2"/>
@@ -1423,19 +1603,23 @@
       <c r="X18" s="2"/>
       <c r="Y18" s="2"/>
     </row>
-    <row r="19" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="18">
         <v>5</v>
       </c>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32"/>
-      <c r="D19" s="31"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="27"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="29"/>
-      <c r="I19" s="27"/>
-      <c r="J19" s="30"/>
+      <c r="B19" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="C19" s="33"/>
+      <c r="D19" s="34" t="s">
+        <v>23</v>
+      </c>
+      <c r="E19" s="33"/>
+      <c r="F19" s="48"/>
+      <c r="G19" s="49"/>
+      <c r="H19" s="50"/>
+      <c r="I19" s="48"/>
+      <c r="J19" s="51"/>
       <c r="K19" s="2"/>
       <c r="L19" s="2"/>
       <c r="M19" s="2"/>
@@ -1452,19 +1636,23 @@
       <c r="X19" s="2"/>
       <c r="Y19" s="2"/>
     </row>
-    <row r="20" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="18">
         <v>6</v>
       </c>
-      <c r="B20" s="31"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="31"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="27"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="29"/>
-      <c r="I20" s="27"/>
-      <c r="J20" s="30"/>
+      <c r="B20" s="34" t="s">
+        <v>53</v>
+      </c>
+      <c r="C20" s="33"/>
+      <c r="D20" s="34" t="s">
+        <v>24</v>
+      </c>
+      <c r="E20" s="33"/>
+      <c r="F20" s="48"/>
+      <c r="G20" s="49"/>
+      <c r="H20" s="50"/>
+      <c r="I20" s="48"/>
+      <c r="J20" s="51"/>
       <c r="K20" s="2"/>
       <c r="L20" s="2"/>
       <c r="M20" s="2"/>
@@ -1481,19 +1669,23 @@
       <c r="X20" s="2"/>
       <c r="Y20" s="2"/>
     </row>
-    <row r="21" spans="1:25" ht="45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:25" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="18">
         <v>7</v>
       </c>
-      <c r="B21" s="31"/>
-      <c r="C21" s="32"/>
-      <c r="D21" s="31"/>
-      <c r="E21" s="32"/>
-      <c r="F21" s="27"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="29"/>
-      <c r="I21" s="27"/>
-      <c r="J21" s="30"/>
+      <c r="B21" s="34" t="s">
+        <v>25</v>
+      </c>
+      <c r="C21" s="33"/>
+      <c r="D21" s="34" t="s">
+        <v>26</v>
+      </c>
+      <c r="E21" s="33"/>
+      <c r="F21" s="48"/>
+      <c r="G21" s="49"/>
+      <c r="H21" s="50"/>
+      <c r="I21" s="48"/>
+      <c r="J21" s="51"/>
       <c r="K21" s="2"/>
       <c r="L21" s="2"/>
       <c r="M21" s="2"/>
@@ -1510,19 +1702,23 @@
       <c r="X21" s="2"/>
       <c r="Y21" s="2"/>
     </row>
-    <row r="22" spans="1:25" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="18">
         <v>8</v>
       </c>
-      <c r="B22" s="31"/>
-      <c r="C22" s="32"/>
-      <c r="D22" s="31"/>
-      <c r="E22" s="32"/>
-      <c r="F22" s="27"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="29"/>
-      <c r="I22" s="27"/>
-      <c r="J22" s="30"/>
+      <c r="B22" s="34" t="s">
+        <v>56</v>
+      </c>
+      <c r="C22" s="33"/>
+      <c r="D22" s="34" t="s">
+        <v>27</v>
+      </c>
+      <c r="E22" s="33"/>
+      <c r="F22" s="48"/>
+      <c r="G22" s="49"/>
+      <c r="H22" s="50"/>
+      <c r="I22" s="48"/>
+      <c r="J22" s="51"/>
       <c r="K22" s="2"/>
       <c r="L22" s="2"/>
       <c r="M22" s="2"/>
@@ -1543,17 +1739,19 @@
       <c r="A23" s="18">
         <v>9</v>
       </c>
-      <c r="B23" s="31" t="s">
-        <v>21</v>
+      <c r="B23" s="34" t="s">
+        <v>28</v>
       </c>
-      <c r="C23" s="32"/>
-      <c r="D23" s="31"/>
-      <c r="E23" s="32"/>
-      <c r="F23" s="27"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="29"/>
-      <c r="I23" s="27"/>
-      <c r="J23" s="30"/>
+      <c r="C23" s="33"/>
+      <c r="D23" s="34" t="s">
+        <v>29</v>
+      </c>
+      <c r="E23" s="33"/>
+      <c r="F23" s="48"/>
+      <c r="G23" s="49"/>
+      <c r="H23" s="50"/>
+      <c r="I23" s="48"/>
+      <c r="J23" s="51"/>
       <c r="K23" s="2"/>
       <c r="L23" s="2"/>
       <c r="M23" s="2"/>
@@ -1570,19 +1768,23 @@
       <c r="X23" s="2"/>
       <c r="Y23" s="2"/>
     </row>
-    <row r="24" spans="1:25" ht="36" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:25" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="18">
         <v>10</v>
       </c>
-      <c r="B24" s="31"/>
-      <c r="C24" s="32"/>
-      <c r="D24" s="31"/>
-      <c r="E24" s="32"/>
-      <c r="F24" s="27"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="29"/>
-      <c r="I24" s="27"/>
-      <c r="J24" s="30"/>
+      <c r="B24" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="C24" s="33"/>
+      <c r="D24" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E24" s="33"/>
+      <c r="F24" s="48"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="50"/>
+      <c r="I24" s="48"/>
+      <c r="J24" s="51"/>
       <c r="K24" s="2"/>
       <c r="L24" s="2"/>
       <c r="M24" s="2"/>
@@ -1599,19 +1801,23 @@
       <c r="X24" s="2"/>
       <c r="Y24" s="2"/>
     </row>
-    <row r="25" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="18">
         <v>11</v>
       </c>
-      <c r="B25" s="31"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="31"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="27"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="29"/>
-      <c r="I25" s="27"/>
-      <c r="J25" s="30"/>
+      <c r="B25" s="34" t="s">
+        <v>31</v>
+      </c>
+      <c r="C25" s="33"/>
+      <c r="D25" s="34" t="s">
+        <v>32</v>
+      </c>
+      <c r="E25" s="33"/>
+      <c r="F25" s="48"/>
+      <c r="G25" s="49"/>
+      <c r="H25" s="50"/>
+      <c r="I25" s="48"/>
+      <c r="J25" s="51"/>
       <c r="K25" s="2"/>
       <c r="L25" s="2"/>
       <c r="M25" s="2"/>
@@ -1628,19 +1834,23 @@
       <c r="X25" s="2"/>
       <c r="Y25" s="2"/>
     </row>
-    <row r="26" spans="1:25" ht="42.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:25" ht="48" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="18">
         <v>12</v>
       </c>
-      <c r="B26" s="31"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="31"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="27"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="29"/>
-      <c r="I26" s="27"/>
-      <c r="J26" s="30"/>
+      <c r="B26" s="34" t="s">
+        <v>54</v>
+      </c>
+      <c r="C26" s="33"/>
+      <c r="D26" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E26" s="33"/>
+      <c r="F26" s="48"/>
+      <c r="G26" s="49"/>
+      <c r="H26" s="50"/>
+      <c r="I26" s="48"/>
+      <c r="J26" s="51"/>
       <c r="K26" s="2"/>
       <c r="L26" s="2"/>
       <c r="M26" s="2"/>
@@ -1657,19 +1867,23 @@
       <c r="X26" s="2"/>
       <c r="Y26" s="2"/>
     </row>
-    <row r="27" spans="1:25" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="18">
         <v>13</v>
       </c>
-      <c r="B27" s="31"/>
-      <c r="C27" s="32"/>
-      <c r="D27" s="31"/>
-      <c r="E27" s="32"/>
-      <c r="F27" s="27"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="29"/>
-      <c r="I27" s="27"/>
-      <c r="J27" s="30"/>
+      <c r="B27" s="34" t="s">
+        <v>34</v>
+      </c>
+      <c r="C27" s="33"/>
+      <c r="D27" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E27" s="33"/>
+      <c r="F27" s="48"/>
+      <c r="G27" s="49"/>
+      <c r="H27" s="50"/>
+      <c r="I27" s="48"/>
+      <c r="J27" s="51"/>
       <c r="K27" s="2"/>
       <c r="L27" s="2"/>
       <c r="M27" s="2"/>
@@ -1686,19 +1900,23 @@
       <c r="X27" s="2"/>
       <c r="Y27" s="2"/>
     </row>
-    <row r="28" spans="1:25" ht="35.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="18">
         <v>14</v>
       </c>
-      <c r="B28" s="31"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="31"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="27"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="29"/>
-      <c r="I28" s="27"/>
-      <c r="J28" s="30"/>
+      <c r="B28" s="34" t="s">
+        <v>35</v>
+      </c>
+      <c r="C28" s="33"/>
+      <c r="D28" s="34" t="s">
+        <v>33</v>
+      </c>
+      <c r="E28" s="33"/>
+      <c r="F28" s="48"/>
+      <c r="G28" s="49"/>
+      <c r="H28" s="50"/>
+      <c r="I28" s="48"/>
+      <c r="J28" s="51"/>
       <c r="K28" s="2"/>
       <c r="L28" s="2"/>
       <c r="M28" s="2"/>
@@ -1715,19 +1933,23 @@
       <c r="X28" s="2"/>
       <c r="Y28" s="2"/>
     </row>
-    <row r="29" spans="1:25" ht="46.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:25" ht="48.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="18">
         <v>15</v>
       </c>
-      <c r="B29" s="31"/>
-      <c r="C29" s="32"/>
-      <c r="D29" s="31"/>
-      <c r="E29" s="32"/>
-      <c r="F29" s="27"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="29"/>
-      <c r="I29" s="27"/>
-      <c r="J29" s="30"/>
+      <c r="B29" s="34" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="33"/>
+      <c r="D29" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="E29" s="33"/>
+      <c r="F29" s="48"/>
+      <c r="G29" s="49"/>
+      <c r="H29" s="50"/>
+      <c r="I29" s="48"/>
+      <c r="J29" s="51"/>
       <c r="K29" s="2"/>
       <c r="L29" s="2"/>
       <c r="M29" s="2"/>
@@ -1744,19 +1966,23 @@
       <c r="X29" s="2"/>
       <c r="Y29" s="2"/>
     </row>
-    <row r="30" spans="1:25" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:25" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="18">
         <v>16</v>
       </c>
-      <c r="B30" s="31"/>
-      <c r="C30" s="32"/>
-      <c r="D30" s="31"/>
-      <c r="E30" s="32"/>
-      <c r="F30" s="27"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="29"/>
-      <c r="I30" s="27"/>
-      <c r="J30" s="30"/>
+      <c r="B30" s="34" t="s">
+        <v>38</v>
+      </c>
+      <c r="C30" s="33"/>
+      <c r="D30" s="34" t="s">
+        <v>37</v>
+      </c>
+      <c r="E30" s="33"/>
+      <c r="F30" s="48"/>
+      <c r="G30" s="49"/>
+      <c r="H30" s="50"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="51"/>
       <c r="K30" s="2"/>
       <c r="L30" s="2"/>
       <c r="M30" s="2"/>
@@ -1777,15 +2003,19 @@
       <c r="A31" s="18">
         <v>17</v>
       </c>
-      <c r="B31" s="31"/>
-      <c r="C31" s="32"/>
-      <c r="D31" s="31"/>
-      <c r="E31" s="32"/>
-      <c r="F31" s="27"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="29"/>
-      <c r="I31" s="27"/>
-      <c r="J31" s="30"/>
+      <c r="B31" s="34" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="33"/>
+      <c r="D31" s="34" t="s">
+        <v>40</v>
+      </c>
+      <c r="E31" s="33"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="49"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="48"/>
+      <c r="J31" s="51"/>
       <c r="K31" s="2"/>
       <c r="L31" s="2"/>
       <c r="M31" s="2"/>
@@ -1806,15 +2036,19 @@
       <c r="A32" s="18">
         <v>18</v>
       </c>
-      <c r="B32" s="31"/>
-      <c r="C32" s="32"/>
-      <c r="D32" s="31"/>
-      <c r="E32" s="32"/>
-      <c r="F32" s="27"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="29"/>
-      <c r="I32" s="27"/>
-      <c r="J32" s="30"/>
+      <c r="B32" s="34" t="s">
+        <v>41</v>
+      </c>
+      <c r="C32" s="33"/>
+      <c r="D32" s="34" t="s">
+        <v>42</v>
+      </c>
+      <c r="E32" s="33"/>
+      <c r="F32" s="48"/>
+      <c r="G32" s="49"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="48"/>
+      <c r="J32" s="51"/>
       <c r="K32" s="2"/>
       <c r="L32" s="2"/>
       <c r="M32" s="2"/>
@@ -1831,19 +2065,23 @@
       <c r="X32" s="2"/>
       <c r="Y32" s="2"/>
     </row>
-    <row r="33" spans="1:25" ht="44.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:25" ht="47.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="18">
         <v>19</v>
       </c>
-      <c r="B33" s="31"/>
-      <c r="C33" s="32"/>
-      <c r="D33" s="31"/>
-      <c r="E33" s="32"/>
-      <c r="F33" s="27"/>
-      <c r="G33" s="28"/>
-      <c r="H33" s="29"/>
-      <c r="I33" s="27"/>
-      <c r="J33" s="30"/>
+      <c r="B33" s="34" t="s">
+        <v>43</v>
+      </c>
+      <c r="C33" s="33"/>
+      <c r="D33" s="34" t="s">
+        <v>44</v>
+      </c>
+      <c r="E33" s="33"/>
+      <c r="F33" s="48"/>
+      <c r="G33" s="49"/>
+      <c r="H33" s="50"/>
+      <c r="I33" s="48"/>
+      <c r="J33" s="51"/>
       <c r="K33" s="2"/>
       <c r="L33" s="2"/>
       <c r="M33" s="2"/>
@@ -1860,19 +2098,23 @@
       <c r="X33" s="2"/>
       <c r="Y33" s="2"/>
     </row>
-    <row r="34" spans="1:25" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:25" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="20">
         <v>20</v>
       </c>
-      <c r="B34" s="33"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="33"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="35"/>
-      <c r="G34" s="36"/>
-      <c r="H34" s="37"/>
-      <c r="I34" s="35"/>
-      <c r="J34" s="38"/>
+      <c r="B34" s="40" t="s">
+        <v>59</v>
+      </c>
+      <c r="C34" s="42"/>
+      <c r="D34" s="40" t="s">
+        <v>45</v>
+      </c>
+      <c r="E34" s="42"/>
+      <c r="F34" s="54"/>
+      <c r="G34" s="55"/>
+      <c r="H34" s="56"/>
+      <c r="I34" s="54"/>
+      <c r="J34" s="57"/>
       <c r="K34" s="2"/>
       <c r="L34" s="2"/>
       <c r="M34" s="2"/>
@@ -27811,38 +28053,54 @@
     </row>
   </sheetData>
   <mergeCells count="104">
-    <mergeCell ref="A1:B1"/>
-    <mergeCell ref="F1:J1"/>
-    <mergeCell ref="A2:B2"/>
-    <mergeCell ref="F2:G2"/>
-    <mergeCell ref="H2:I2"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="G7:J7"/>
-    <mergeCell ref="G8:J8"/>
-    <mergeCell ref="A3:B3"/>
-    <mergeCell ref="B5:D5"/>
-    <mergeCell ref="G5:J5"/>
-    <mergeCell ref="B6:D6"/>
-    <mergeCell ref="G6:J6"/>
-    <mergeCell ref="B7:D7"/>
-    <mergeCell ref="B8:D8"/>
-    <mergeCell ref="B9:D9"/>
-    <mergeCell ref="G9:J9"/>
-    <mergeCell ref="B11:J11"/>
-    <mergeCell ref="B12:J12"/>
-    <mergeCell ref="D14:E14"/>
-    <mergeCell ref="F14:H14"/>
-    <mergeCell ref="I14:J14"/>
-    <mergeCell ref="F16:H16"/>
-    <mergeCell ref="I16:J16"/>
-    <mergeCell ref="B14:C14"/>
-    <mergeCell ref="B15:C15"/>
-    <mergeCell ref="D15:E15"/>
-    <mergeCell ref="F15:H15"/>
-    <mergeCell ref="I15:J15"/>
-    <mergeCell ref="B16:C16"/>
-    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="F23:H23"/>
+    <mergeCell ref="I23:J23"/>
+    <mergeCell ref="B24:C24"/>
+    <mergeCell ref="D24:E24"/>
+    <mergeCell ref="F28:H28"/>
+    <mergeCell ref="I28:J28"/>
+    <mergeCell ref="D34:E34"/>
+    <mergeCell ref="F34:H34"/>
+    <mergeCell ref="F32:H32"/>
+    <mergeCell ref="I32:J32"/>
+    <mergeCell ref="B33:C33"/>
+    <mergeCell ref="D33:E33"/>
+    <mergeCell ref="F33:H33"/>
+    <mergeCell ref="I33:J33"/>
+    <mergeCell ref="B34:C34"/>
+    <mergeCell ref="I34:J34"/>
+    <mergeCell ref="D30:E30"/>
+    <mergeCell ref="F30:H30"/>
+    <mergeCell ref="I30:J30"/>
+    <mergeCell ref="B30:C30"/>
+    <mergeCell ref="B31:C31"/>
+    <mergeCell ref="D31:E31"/>
+    <mergeCell ref="F31:H31"/>
+    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="D17:E17"/>
+    <mergeCell ref="F17:H17"/>
+    <mergeCell ref="I17:J17"/>
+    <mergeCell ref="D18:E18"/>
+    <mergeCell ref="F18:H18"/>
+    <mergeCell ref="I18:J18"/>
+    <mergeCell ref="B18:C18"/>
+    <mergeCell ref="B19:C19"/>
+    <mergeCell ref="D19:E19"/>
+    <mergeCell ref="F19:H19"/>
+    <mergeCell ref="I19:J19"/>
+    <mergeCell ref="B32:C32"/>
+    <mergeCell ref="D32:E32"/>
+    <mergeCell ref="B27:C27"/>
+    <mergeCell ref="D27:E27"/>
+    <mergeCell ref="F27:H27"/>
+    <mergeCell ref="I27:J27"/>
+    <mergeCell ref="B28:C28"/>
+    <mergeCell ref="D28:E28"/>
+    <mergeCell ref="B29:C29"/>
+    <mergeCell ref="D29:E29"/>
+    <mergeCell ref="F29:H29"/>
+    <mergeCell ref="I29:J29"/>
     <mergeCell ref="F20:H20"/>
     <mergeCell ref="I20:J20"/>
     <mergeCell ref="B25:C25"/>
@@ -27867,56 +28125,41 @@
     <mergeCell ref="B22:C22"/>
     <mergeCell ref="B23:C23"/>
     <mergeCell ref="D23:E23"/>
-    <mergeCell ref="B32:C32"/>
-    <mergeCell ref="D32:E32"/>
-    <mergeCell ref="B27:C27"/>
-    <mergeCell ref="D27:E27"/>
-    <mergeCell ref="F27:H27"/>
-    <mergeCell ref="I27:J27"/>
-    <mergeCell ref="B28:C28"/>
-    <mergeCell ref="D28:E28"/>
-    <mergeCell ref="B29:C29"/>
-    <mergeCell ref="D29:E29"/>
-    <mergeCell ref="F29:H29"/>
-    <mergeCell ref="I29:J29"/>
-    <mergeCell ref="B17:C17"/>
-    <mergeCell ref="D17:E17"/>
-    <mergeCell ref="F17:H17"/>
-    <mergeCell ref="I17:J17"/>
-    <mergeCell ref="D18:E18"/>
-    <mergeCell ref="F18:H18"/>
-    <mergeCell ref="I18:J18"/>
-    <mergeCell ref="B18:C18"/>
-    <mergeCell ref="B19:C19"/>
-    <mergeCell ref="D19:E19"/>
-    <mergeCell ref="F19:H19"/>
-    <mergeCell ref="I19:J19"/>
-    <mergeCell ref="F23:H23"/>
-    <mergeCell ref="I23:J23"/>
-    <mergeCell ref="B24:C24"/>
-    <mergeCell ref="D24:E24"/>
-    <mergeCell ref="F28:H28"/>
-    <mergeCell ref="I28:J28"/>
-    <mergeCell ref="D34:E34"/>
-    <mergeCell ref="F34:H34"/>
-    <mergeCell ref="F32:H32"/>
-    <mergeCell ref="I32:J32"/>
-    <mergeCell ref="B33:C33"/>
-    <mergeCell ref="D33:E33"/>
-    <mergeCell ref="F33:H33"/>
-    <mergeCell ref="I33:J33"/>
-    <mergeCell ref="B34:C34"/>
-    <mergeCell ref="I34:J34"/>
-    <mergeCell ref="D30:E30"/>
-    <mergeCell ref="F30:H30"/>
-    <mergeCell ref="I30:J30"/>
-    <mergeCell ref="B30:C30"/>
-    <mergeCell ref="B31:C31"/>
-    <mergeCell ref="D31:E31"/>
-    <mergeCell ref="F31:H31"/>
-    <mergeCell ref="I31:J31"/>
+    <mergeCell ref="B9:D9"/>
+    <mergeCell ref="G9:J9"/>
+    <mergeCell ref="B11:J11"/>
+    <mergeCell ref="B12:J12"/>
+    <mergeCell ref="D14:E14"/>
+    <mergeCell ref="F14:H14"/>
+    <mergeCell ref="I14:J14"/>
+    <mergeCell ref="F16:H16"/>
+    <mergeCell ref="I16:J16"/>
+    <mergeCell ref="B14:C14"/>
+    <mergeCell ref="B15:C15"/>
+    <mergeCell ref="D15:E15"/>
+    <mergeCell ref="F15:H15"/>
+    <mergeCell ref="I15:J15"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="D16:E16"/>
+    <mergeCell ref="A1:B1"/>
+    <mergeCell ref="F1:J1"/>
+    <mergeCell ref="A2:B2"/>
+    <mergeCell ref="F2:G2"/>
+    <mergeCell ref="H2:I2"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="G7:J7"/>
+    <mergeCell ref="G8:J8"/>
+    <mergeCell ref="A3:B3"/>
+    <mergeCell ref="B5:D5"/>
+    <mergeCell ref="G5:J5"/>
+    <mergeCell ref="B6:D6"/>
+    <mergeCell ref="G6:J6"/>
+    <mergeCell ref="B7:D7"/>
+    <mergeCell ref="B8:D8"/>
   </mergeCells>
   <pageMargins left="1" right="1" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>